--- a/data/xlsx/sbce_config_kvm_ems1_sbce1_ems2_sbce2_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems1_sbce1_ems2_sbce2_template.xlsx
@@ -10,8 +10,6 @@
   <sheets>
     <sheet name="EMS1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="SBCE1" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="EMS2" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="SBCE2" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="127">
   <si>
     <t xml:space="preserve">platform_type</t>
   </si>
@@ -404,24 +402,6 @@
   </si>
   <si>
     <t xml:space="preserve">10.10.11.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ems2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.10.10.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sbce2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sbce2app</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.10.10.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.10.11.20</t>
   </si>
 </sst>
 </file>
@@ -1539,23 +1519,23 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>$B$1="ESXI"</formula1>
+      <formula1>#REF!="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#REF!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+      <formula1>#REF!&lt;&gt;"SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B47" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula1>#REF!&lt;&gt;"EMS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>$B$10="SBCE"</formula1>
+      <formula1>#REF!="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
@@ -2227,19 +2207,19 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>$B$1="ESXI"</formula1>
+      <formula1>#REF!="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#REF!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+      <formula1>#REF!&lt;&gt;"SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>$B$10="SBCE"</formula1>
+      <formula1>#REF!="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
@@ -2255,1377 +2235,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B47" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C1048576"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.78"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT(B9, ".", B20)</f>
-        <v>ems2.lab.local</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>B10&lt;&gt;"EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B47">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>B10="EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>B10="EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B45">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>B10="EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>B10&lt;&gt;"SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
-      <formula>B10&lt;&gt;"SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
-      <formula>B10="EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B41">
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>B10="EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B40">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>B10="EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>B10="EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
-      <formula>B10="EMS+SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
-      <formula>B10="EMS+SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
-      <formula>B10="SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B25">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
-      <formula>B10="SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
-      <formula>B10="SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
-      <formula>B10="SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>B10="SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
-      <formula>B10="SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
-      <formula>B10="EMS+SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
-    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
-      <formula>B1="KVM"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="15">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B8" type="list">
-      <formula1>"DUAL_STACK,IPV4"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
-      <formula1>21</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
-      <formula1>"ESXI,KVM"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
-      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
-      <formula1>"primary,secondary"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
-      <formula1>"A1,A2,B1,B2"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>$B$1="ESXI"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B47" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>$B$10="SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
-      <formula1>7</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
-      <formula1>8</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="115.74"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT(B9, ".", B20)</f>
-        <v>sbce2.lab.local</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>B10&lt;&gt;"EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B47">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>B10="EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>B10="EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B45">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>B10="EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>B10&lt;&gt;"SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
-      <formula>B10&lt;&gt;"SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
-      <formula>B10="EMS+SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>B10="EMS+SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>B10="SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B25">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>B10="SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
-      <formula>B10="SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
-      <formula>B10="SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
-      <formula>B10="SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
-      <formula>B10="SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
-      <formula>B10="EMS+SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
-      <formula>B1="KVM"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="15">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B8" type="list">
-      <formula1>"DUAL_STACK,IPV4"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
-      <formula1>21</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
-      <formula1>"ESXI,KVM"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
-      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
-      <formula1>"primary,secondary"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
-      <formula1>"A1,A2,B1,B2"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>$B$1="ESXI"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>$B$10="SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
-      <formula1>7</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
-      <formula1>8</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B47" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula1>#REF!&lt;&gt;"EMS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/data/xlsx/sbce_config_kvm_ems1_sbce1_ems2_sbce2_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems1_sbce1_ems2_sbce2_template.xlsx
@@ -5,11 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="EMS1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="SBCE1" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="EMS2" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="SBCE2" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="133">
   <si>
     <t xml:space="preserve">platform_type</t>
   </si>
@@ -402,6 +404,24 @@
   </si>
   <si>
     <t xml:space="preserve">10.10.11.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ems2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10.10.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sbce2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sbce2app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10.10.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10.11.11</t>
   </si>
 </sst>
 </file>
@@ -1519,23 +1539,23 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>#REF!="ESXI"</formula1>
+      <formula1>#ref!="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>#REF!&lt;&gt;"SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B47" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>#REF!="SBCE"</formula1>
+      <formula1>#ref!="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
@@ -2207,19 +2227,19 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>#REF!="ESXI"</formula1>
+      <formula1>#ref!="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>#REF!&lt;&gt;"SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>#REF!="SBCE"</formula1>
+      <formula1>#ref!="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
@@ -2235,7 +2255,1380 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B47" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C1048576"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.78"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(B9, ".", B20)</f>
+        <v>ems2.lab.local</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>B10&lt;&gt;"EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>B10&lt;&gt;"SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>B10&lt;&gt;"SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+      <formula>B1="KVM"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="15">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B8" type="list">
+      <formula1>"DUAL_STACK,IPV4"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
+      <formula1>21</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
+      <formula1>"ESXI,KVM"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
+      <formula1>"primary,secondary"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
+      <formula1>"A1,A2,B1,B2"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
+      <formula1>#ref!="ESXI"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
+      <formula1>#ref!&lt;&gt;"SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B47" type="custom">
+      <formula1>#ref!&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
+      <formula1>#ref!="SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
+      <formula1>7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
+      <formula1>8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="115.74"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(B9, ".", B20)</f>
+        <v>sbce2.lab.local</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>B10&lt;&gt;"EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>B10&lt;&gt;"SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>B10&lt;&gt;"SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>B1="KVM"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="16">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B8" type="list">
+      <formula1>"DUAL_STACK,IPV4"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
+      <formula1>21</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
+      <formula1>"ESXI,KVM"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
+      <formula1>"primary,secondary"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
+      <formula1>"A1,A2,B1,B2"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
+      <formula1>#ref!="ESXI"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B32" type="custom">
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
+      <formula1>#ref!&lt;&gt;"SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
+      <formula1>#ref!="SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
+      <formula1>7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
+      <formula1>8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B47" type="custom">
+      <formula1>#ref!&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31" type="none">
+      <formula1>#REF!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/data/xlsx/sbce_config_kvm_ems1_sbce1_ems2_sbce2_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems1_sbce1_ems2_sbce2_template.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="134">
   <si>
     <t xml:space="preserve">platform_type</t>
   </si>
@@ -247,154 +247,157 @@
     <t xml:space="preserve">Time Zone - Time Zone in which device is located  (for example America/Edmonton)</t>
   </si>
   <si>
-    <t xml:space="preserve">ntpservers</t>
+    <t xml:space="preserve">ntpserver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NTP Server Address: - The IPv4 address for NTP servers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ntpipv6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NTP Server Address IPv6: - (For DUAL_STACK Mode Only) The IPv6 address for NTP server.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNS Address: - The IPv4 address list for DNS servers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emsip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMS IP Address: (*) - IPv4 address of the EMS System. (Not for Primary EMS and SingleBox deployments.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emsip_v6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Optional)EMS IPv6 Address: - IPv6 address for the EMS System.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rootpass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">r00t10_cmb@Dm1n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root Password (*) - root password for Device.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ipcspass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sbc10_cmb@Dm1n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ipcs Password: (*) - ipcs password for Device.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grubpass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grub password: (*) - grub password for Device.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ucsecpass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web ucsec account password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1 NIC Port-group / Bridge name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2 NIC Port-group / Bridge name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1 NIC Port-group / Bridge name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 NIC Port-group / Bridge name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1 NIC Port-group / Bridge name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2 NIC Port-group / Bridge name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ha_peer_node</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HA Peer SBCE name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ha_peer_ip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HA Peer SBCE IP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sig_iface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIP data interace (A1, A2, B1, B2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sig_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIP data interface name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sig_mask</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIP data interface mask</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sig_gw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIP data interface default gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sig_ip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIP data interface IP address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sbce1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sbce1app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10.10.11</t>
   </si>
   <si>
     <t xml:space="preserve">NTP Server Address: - The IPv4 address for NTP servers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ntpipv6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NTP Server Address IPv6: - (For DUAL_STACK Mode Only) The IPv6 address for NTP server.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNS Address: - The IPv4 address list for DNS servers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emsip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMS IP Address: (*) - IPv4 address of the EMS System. (Not for Primary EMS and SingleBox deployments.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emsip_v6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Optional)EMS IPv6 Address: - IPv6 address for the EMS System.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rootpass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">r00t10_cmb@Dm1n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root Password (*) - root password for Device.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ipcspass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sbc10_cmb@Dm1n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ipcs Password: (*) - ipcs password for Device.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grubpass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grub password: (*) - grub password for Device.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ucsecpass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Web ucsec account password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1 NIC Port-group / Bridge name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2 NIC Port-group / Bridge name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A1 NIC Port-group / Bridge name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A2 NIC Port-group / Bridge name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1 NIC Port-group / Bridge name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B2 NIC Port-group / Bridge name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ha_peer_node</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HA Peer SBCE name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ha_peer_ip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HA Peer SBCE IP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sig_iface</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIP data interace (A1, A2, B1, B2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sig_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIP data interface name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sig_mask</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIP data interface mask</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sig_gw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIP data interface default gateway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sig_ip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIP data interface IP address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sbce1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SBCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sbce1app</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.10.10.11</t>
   </si>
   <si>
     <t xml:space="preserve">A1_sig</t>
@@ -431,7 +434,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -453,6 +456,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -497,7 +506,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -512,6 +521,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -909,7 +922,7 @@
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="49.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.78"/>
   </cols>
   <sheetData>
@@ -1887,14 +1900,14 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="4" t="s">
         <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2077,7 +2090,7 @@
         <v>112</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>113</v>
@@ -2099,7 +2112,7 @@
         <v>116</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>117</v>
@@ -2110,7 +2123,7 @@
         <v>118</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>119</v>
@@ -2353,7 +2366,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -2375,7 +2388,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>25</v>
@@ -2397,7 +2410,7 @@
         <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
@@ -2430,7 +2443,7 @@
         <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>39</v>
@@ -2575,14 +2588,14 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="4" t="s">
         <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3034,7 +3047,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -3056,7 +3069,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>25</v>
@@ -3078,7 +3091,7 @@
         <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
@@ -3111,7 +3124,7 @@
         <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>39</v>
@@ -3256,14 +3269,14 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="4" t="s">
         <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3290,7 +3303,7 @@
         <v>80</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>81</v>
@@ -3446,7 +3459,7 @@
         <v>112</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>113</v>
@@ -3468,7 +3481,7 @@
         <v>116</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>117</v>
@@ -3479,7 +3492,7 @@
         <v>118</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>119</v>
@@ -3628,7 +3641,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31" type="none">
-      <formula1>#REF!&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
